--- a/docs/xlsx/plan-revision-hu.xlsx
+++ b/docs/xlsx/plan-revision-hu.xlsx
@@ -4052,7 +4052,7 @@
       <c r="J9" s="17" t="n"/>
       <c r="K9" s="17" t="n"/>
       <c r="L9" s="16" t="n"/>
-      <c r="M9" s="21" t="n"/>
+      <c r="M9" s="16" t="n"/>
       <c r="N9" s="21" t="n"/>
       <c r="O9" s="21" t="n"/>
       <c r="P9" s="21" t="n"/>
@@ -4184,7 +4184,7 @@
       <c r="Q12" s="17" t="n"/>
       <c r="R12" s="17" t="n"/>
       <c r="S12" s="16" t="n"/>
-      <c r="T12" s="21" t="n"/>
+      <c r="T12" s="16" t="n"/>
       <c r="U12" s="21" t="n"/>
       <c r="V12" s="21" t="n"/>
       <c r="W12" s="21" t="n"/>
